--- a/Data/EXCEL/Transfer/salemon/202206/6617-salemon-202206.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202206/6617-salemon-202206.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linea\OneDrive\myStocksPGMs\V2.0\xls2xlsx\transfer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKSPACES\myStocksPGMs\V2.0\xls2xlsx\transfer\202206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2FC75F6-CD58-4306-A76D-FF921B542B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{13049BF5-803E-499D-904D-D4813087034F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2625" windowWidth="24465" windowHeight="12855"/>
+    <workbookView xWindow="945" yWindow="3600" windowWidth="26925" windowHeight="11205"/>
   </bookViews>
   <sheets>
     <sheet name="6617-salemon-202206" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="18">
   <si>
     <t>月別</t>
   </si>
@@ -261,7 +261,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF008000"/>
+      <color rgb="FFFF0000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -277,7 +277,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF008000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -1218,20 +1218,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:Q70"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.875" customWidth="1"/>
-    <col min="2" max="5" width="10.75" customWidth="1"/>
-    <col min="6" max="7" width="11.75" customWidth="1"/>
-    <col min="8" max="8" width="12.25" customWidth="1"/>
-    <col min="9" max="10" width="10.25" customWidth="1"/>
-    <col min="11" max="11" width="12.25" customWidth="1"/>
-    <col min="12" max="12" width="10.75" customWidth="1"/>
-    <col min="13" max="13" width="12.25" customWidth="1"/>
-    <col min="14" max="15" width="10.25" customWidth="1"/>
-    <col min="16" max="16" width="12.25" customWidth="1"/>
-    <col min="17" max="17" width="12.125" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="5" width="11.75" customWidth="1"/>
+    <col min="6" max="7" width="12.875" customWidth="1"/>
+    <col min="8" max="8" width="13.5" customWidth="1"/>
+    <col min="9" max="10" width="11.25" customWidth="1"/>
+    <col min="11" max="11" width="13.5" customWidth="1"/>
+    <col min="12" max="12" width="11.75" customWidth="1"/>
+    <col min="13" max="13" width="13.5" customWidth="1"/>
+    <col min="14" max="15" width="11.25" customWidth="1"/>
+    <col min="16" max="16" width="13.5" customWidth="1"/>
+    <col min="17" max="17" width="12.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1384,25 +1384,25 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B5" s="7">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C5" s="7">
-        <v>258</v>
+        <v>289.5</v>
       </c>
       <c r="D5" s="7">
-        <v>276</v>
+        <v>292.5</v>
       </c>
       <c r="E5" s="7">
-        <v>240.5</v>
+        <v>247.5</v>
       </c>
       <c r="F5" s="8">
-        <v>-6</v>
+        <v>31.5</v>
       </c>
       <c r="G5" s="8">
-        <v>-2.27</v>
+        <v>12.21</v>
       </c>
       <c r="H5" s="9">
         <v>0</v>
@@ -1437,25 +1437,25 @@
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B6" s="7">
-        <v>249.5</v>
+        <v>264</v>
       </c>
       <c r="C6" s="7">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="D6" s="7">
-        <v>265.5</v>
+        <v>276</v>
       </c>
       <c r="E6" s="7">
-        <v>242.5</v>
+        <v>240.5</v>
       </c>
       <c r="F6" s="10">
-        <v>14.5</v>
+        <v>-6</v>
       </c>
       <c r="G6" s="10">
-        <v>5.81</v>
+        <v>-2.27</v>
       </c>
       <c r="H6" s="9">
         <v>0</v>
@@ -1490,25 +1490,25 @@
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B7" s="7">
-        <v>268.5</v>
+        <v>249.5</v>
       </c>
       <c r="C7" s="7">
-        <v>249.5</v>
+        <v>264</v>
       </c>
       <c r="D7" s="7">
-        <v>268.5</v>
+        <v>265.5</v>
       </c>
       <c r="E7" s="7">
-        <v>229.5</v>
+        <v>242.5</v>
       </c>
       <c r="F7" s="8">
-        <v>-19</v>
+        <v>14.5</v>
       </c>
       <c r="G7" s="8">
-        <v>-7.08</v>
+        <v>5.81</v>
       </c>
       <c r="H7" s="9">
         <v>0</v>
@@ -1543,25 +1543,25 @@
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B8" s="7">
+        <v>268.5</v>
+      </c>
+      <c r="C8" s="7">
         <v>249.5</v>
       </c>
-      <c r="C8" s="7">
+      <c r="D8" s="7">
         <v>268.5</v>
       </c>
-      <c r="D8" s="7">
-        <v>309.5</v>
-      </c>
       <c r="E8" s="7">
-        <v>249.5</v>
+        <v>229.5</v>
       </c>
       <c r="F8" s="10">
-        <v>19</v>
+        <v>-19</v>
       </c>
       <c r="G8" s="10">
-        <v>7.62</v>
+        <v>-7.08</v>
       </c>
       <c r="H8" s="9">
         <v>0</v>
@@ -1596,25 +1596,25 @@
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B9" s="7">
-        <v>283</v>
+        <v>249.5</v>
       </c>
       <c r="C9" s="7">
+        <v>268.5</v>
+      </c>
+      <c r="D9" s="7">
+        <v>309.5</v>
+      </c>
+      <c r="E9" s="7">
         <v>249.5</v>
       </c>
-      <c r="D9" s="7">
-        <v>304.5</v>
-      </c>
-      <c r="E9" s="7">
-        <v>225</v>
-      </c>
       <c r="F9" s="8">
-        <v>-33.5</v>
+        <v>19</v>
       </c>
       <c r="G9" s="8">
-        <v>-11.84</v>
+        <v>7.62</v>
       </c>
       <c r="H9" s="9">
         <v>0</v>
@@ -1649,134 +1649,134 @@
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B10" s="7">
-        <v>239.5</v>
+        <v>283</v>
       </c>
       <c r="C10" s="7">
-        <v>283</v>
+        <v>249.5</v>
       </c>
       <c r="D10" s="7">
-        <v>310</v>
+        <v>304.5</v>
       </c>
       <c r="E10" s="7">
-        <v>231.5</v>
+        <v>225</v>
       </c>
       <c r="F10" s="10">
-        <v>43.5</v>
+        <v>-33.5</v>
       </c>
       <c r="G10" s="10">
-        <v>18.16</v>
+        <v>-11.84</v>
       </c>
       <c r="H10" s="9">
         <v>0</v>
       </c>
-      <c r="I10" s="8">
-        <v>-100</v>
-      </c>
-      <c r="J10" s="8">
-        <v>-100</v>
+      <c r="I10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K10" s="9">
-        <v>1.14E-2</v>
-      </c>
-      <c r="L10" s="10">
-        <v>37.200000000000003</v>
+        <v>0</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="M10" s="9">
         <v>0</v>
       </c>
-      <c r="N10" s="8">
-        <v>-100</v>
-      </c>
-      <c r="O10" s="8">
-        <v>-100</v>
+      <c r="N10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P10" s="9">
-        <v>1.14E-2</v>
-      </c>
-      <c r="Q10" s="10">
-        <v>37.200000000000003</v>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B11" s="7">
-        <v>214.5</v>
+        <v>239.5</v>
       </c>
       <c r="C11" s="7">
-        <v>239.5</v>
+        <v>283</v>
       </c>
       <c r="D11" s="7">
-        <v>239.5</v>
+        <v>310</v>
       </c>
       <c r="E11" s="7">
-        <v>196</v>
-      </c>
-      <c r="F11" s="10">
-        <v>25</v>
-      </c>
-      <c r="G11" s="10">
-        <v>11.66</v>
+        <v>231.5</v>
+      </c>
+      <c r="F11" s="8">
+        <v>43.5</v>
+      </c>
+      <c r="G11" s="8">
+        <v>18.16</v>
       </c>
       <c r="H11" s="9">
-        <v>1.14E-2</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I11" s="10">
+        <v>-100</v>
+      </c>
+      <c r="J11" s="10">
+        <v>-100</v>
       </c>
       <c r="K11" s="9">
         <v>1.14E-2</v>
       </c>
-      <c r="L11" s="9" t="s">
-        <v>17</v>
+      <c r="L11" s="8">
+        <v>37.200000000000003</v>
       </c>
       <c r="M11" s="9">
-        <v>1.14E-2</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O11" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N11" s="10">
+        <v>-100</v>
+      </c>
+      <c r="O11" s="10">
+        <v>-100</v>
       </c>
       <c r="P11" s="9">
         <v>1.14E-2</v>
       </c>
-      <c r="Q11" s="9" t="s">
-        <v>17</v>
+      <c r="Q11" s="8">
+        <v>37.200000000000003</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B12" s="7">
-        <v>234.5</v>
+        <v>214.5</v>
       </c>
       <c r="C12" s="7">
-        <v>214.5</v>
+        <v>239.5</v>
       </c>
       <c r="D12" s="7">
-        <v>234.5</v>
+        <v>239.5</v>
       </c>
       <c r="E12" s="7">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="F12" s="8">
-        <v>-20</v>
+        <v>25</v>
       </c>
       <c r="G12" s="8">
-        <v>-8.5299999999999994</v>
+        <v>11.66</v>
       </c>
       <c r="H12" s="9">
-        <v>0</v>
+        <v>1.14E-2</v>
       </c>
       <c r="I12" s="9" t="s">
         <v>17</v>
@@ -1785,13 +1785,13 @@
         <v>17</v>
       </c>
       <c r="K12" s="9">
-        <v>0</v>
+        <v>1.14E-2</v>
       </c>
       <c r="L12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M12" s="9">
-        <v>0</v>
+        <v>1.14E-2</v>
       </c>
       <c r="N12" s="9" t="s">
         <v>17</v>
@@ -1800,7 +1800,7 @@
         <v>17</v>
       </c>
       <c r="P12" s="9">
-        <v>0</v>
+        <v>1.14E-2</v>
       </c>
       <c r="Q12" s="9" t="s">
         <v>17</v>
@@ -1808,25 +1808,25 @@
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B13" s="7">
-        <v>215.5</v>
+        <v>234.5</v>
       </c>
       <c r="C13" s="7">
+        <v>214.5</v>
+      </c>
+      <c r="D13" s="7">
         <v>234.5</v>
       </c>
-      <c r="D13" s="7">
-        <v>239.5</v>
-      </c>
       <c r="E13" s="7">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="F13" s="10">
-        <v>19</v>
+        <v>-20</v>
       </c>
       <c r="G13" s="10">
-        <v>8.82</v>
+        <v>-8.5299999999999994</v>
       </c>
       <c r="H13" s="9">
         <v>0</v>
@@ -1861,25 +1861,25 @@
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B14" s="7">
-        <v>209.5</v>
+        <v>215.5</v>
       </c>
       <c r="C14" s="7">
-        <v>215.5</v>
+        <v>234.5</v>
       </c>
       <c r="D14" s="7">
-        <v>229.5</v>
+        <v>239.5</v>
       </c>
       <c r="E14" s="7">
-        <v>200.5</v>
-      </c>
-      <c r="F14" s="10">
-        <v>6</v>
-      </c>
-      <c r="G14" s="10">
-        <v>2.86</v>
+        <v>208</v>
+      </c>
+      <c r="F14" s="8">
+        <v>19</v>
+      </c>
+      <c r="G14" s="8">
+        <v>8.82</v>
       </c>
       <c r="H14" s="9">
         <v>0</v>
@@ -1914,25 +1914,25 @@
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B15" s="7">
+        <v>209.5</v>
+      </c>
+      <c r="C15" s="7">
+        <v>215.5</v>
+      </c>
+      <c r="D15" s="7">
         <v>229.5</v>
       </c>
-      <c r="C15" s="7">
-        <v>209.5</v>
-      </c>
-      <c r="D15" s="7">
-        <v>263.5</v>
-      </c>
       <c r="E15" s="7">
-        <v>200</v>
+        <v>200.5</v>
       </c>
       <c r="F15" s="8">
-        <v>-20</v>
+        <v>6</v>
       </c>
       <c r="G15" s="8">
-        <v>-8.7100000000000009</v>
+        <v>2.86</v>
       </c>
       <c r="H15" s="9">
         <v>0</v>
@@ -1967,25 +1967,25 @@
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B16" s="7">
-        <v>193</v>
+        <v>229.5</v>
       </c>
       <c r="C16" s="7">
-        <v>229.5</v>
+        <v>209.5</v>
       </c>
       <c r="D16" s="7">
-        <v>231</v>
+        <v>263.5</v>
       </c>
       <c r="E16" s="7">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="F16" s="10">
-        <v>36.5</v>
+        <v>-20</v>
       </c>
       <c r="G16" s="10">
-        <v>18.91</v>
+        <v>-8.7100000000000009</v>
       </c>
       <c r="H16" s="9">
         <v>0</v>
@@ -2020,25 +2020,25 @@
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B17" s="7">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="C17" s="7">
-        <v>193</v>
+        <v>229.5</v>
       </c>
       <c r="D17" s="7">
-        <v>202.5</v>
+        <v>231</v>
       </c>
       <c r="E17" s="7">
-        <v>150</v>
-      </c>
-      <c r="F17" s="10">
-        <v>15</v>
-      </c>
-      <c r="G17" s="10">
-        <v>8.43</v>
+        <v>179</v>
+      </c>
+      <c r="F17" s="8">
+        <v>36.5</v>
+      </c>
+      <c r="G17" s="8">
+        <v>18.91</v>
       </c>
       <c r="H17" s="9">
         <v>0</v>
@@ -2073,25 +2073,25 @@
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B18" s="7">
-        <v>190.5</v>
+        <v>178</v>
       </c>
       <c r="C18" s="7">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="D18" s="7">
-        <v>225</v>
+        <v>202.5</v>
       </c>
       <c r="E18" s="7">
-        <v>175.5</v>
+        <v>150</v>
       </c>
       <c r="F18" s="8">
-        <v>-12.5</v>
+        <v>15</v>
       </c>
       <c r="G18" s="8">
-        <v>-6.56</v>
+        <v>8.43</v>
       </c>
       <c r="H18" s="9">
         <v>0</v>
@@ -2126,25 +2126,25 @@
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B19" s="7">
-        <v>208.5</v>
+        <v>190.5</v>
       </c>
       <c r="C19" s="7">
-        <v>190.5</v>
+        <v>178</v>
       </c>
       <c r="D19" s="7">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="E19" s="7">
-        <v>175</v>
-      </c>
-      <c r="F19" s="8">
-        <v>-18</v>
-      </c>
-      <c r="G19" s="8">
-        <v>-8.6300000000000008</v>
+        <v>175.5</v>
+      </c>
+      <c r="F19" s="10">
+        <v>-12.5</v>
+      </c>
+      <c r="G19" s="10">
+        <v>-6.56</v>
       </c>
       <c r="H19" s="9">
         <v>0</v>
@@ -2179,25 +2179,25 @@
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B20" s="7">
-        <v>188.5</v>
+        <v>208.5</v>
       </c>
       <c r="C20" s="7">
-        <v>208.5</v>
+        <v>190.5</v>
       </c>
       <c r="D20" s="7">
-        <v>211.5</v>
+        <v>211</v>
       </c>
       <c r="E20" s="7">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="F20" s="10">
-        <v>20</v>
+        <v>-18</v>
       </c>
       <c r="G20" s="10">
-        <v>10.61</v>
+        <v>-8.6300000000000008</v>
       </c>
       <c r="H20" s="9">
         <v>0</v>
@@ -2232,31 +2232,31 @@
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B21" s="7">
-        <v>243</v>
+        <v>188.5</v>
       </c>
       <c r="C21" s="7">
-        <v>188.5</v>
+        <v>208.5</v>
       </c>
       <c r="D21" s="7">
-        <v>254.5</v>
+        <v>211.5</v>
       </c>
       <c r="E21" s="7">
-        <v>174.5</v>
+        <v>140</v>
       </c>
       <c r="F21" s="8">
-        <v>-54.5</v>
+        <v>20</v>
       </c>
       <c r="G21" s="8">
-        <v>-22.43</v>
+        <v>10.61</v>
       </c>
       <c r="H21" s="9">
         <v>0</v>
       </c>
-      <c r="I21" s="8">
-        <v>-100</v>
+      <c r="I21" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J21" s="9" t="s">
         <v>17</v>
@@ -2270,8 +2270,8 @@
       <c r="M21" s="9">
         <v>0</v>
       </c>
-      <c r="N21" s="8">
-        <v>-100</v>
+      <c r="N21" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O21" s="9" t="s">
         <v>17</v>
@@ -2285,81 +2285,81 @@
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B22" s="7">
-        <v>236.5</v>
+        <v>243</v>
       </c>
       <c r="C22" s="7">
-        <v>243</v>
+        <v>188.5</v>
       </c>
       <c r="D22" s="7">
-        <v>269.5</v>
+        <v>254.5</v>
       </c>
       <c r="E22" s="7">
-        <v>228.5</v>
+        <v>174.5</v>
       </c>
       <c r="F22" s="10">
-        <v>6.5</v>
+        <v>-54.5</v>
       </c>
       <c r="G22" s="10">
-        <v>2.75</v>
+        <v>-22.43</v>
       </c>
       <c r="H22" s="9">
-        <v>8.3000000000000001E-3</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I22" s="10">
+        <v>-100</v>
       </c>
       <c r="J22" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K22" s="9">
-        <v>8.3000000000000001E-3</v>
-      </c>
-      <c r="L22" s="10">
-        <v>235.9</v>
+        <v>0</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="M22" s="9">
-        <v>8.3000000000000001E-3</v>
-      </c>
-      <c r="N22" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N22" s="10">
+        <v>-100</v>
       </c>
       <c r="O22" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P22" s="9">
-        <v>8.3000000000000001E-3</v>
-      </c>
-      <c r="Q22" s="10">
-        <v>235.9</v>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B23" s="7">
-        <v>168</v>
+        <v>236.5</v>
       </c>
       <c r="C23" s="7">
-        <v>236.5</v>
+        <v>243</v>
       </c>
       <c r="D23" s="7">
-        <v>254.5</v>
+        <v>269.5</v>
       </c>
       <c r="E23" s="7">
-        <v>162.5</v>
-      </c>
-      <c r="F23" s="10">
-        <v>68.5</v>
-      </c>
-      <c r="G23" s="10">
-        <v>40.770000000000003</v>
+        <v>228.5</v>
+      </c>
+      <c r="F23" s="8">
+        <v>6.5</v>
+      </c>
+      <c r="G23" s="8">
+        <v>2.75</v>
       </c>
       <c r="H23" s="9">
-        <v>0</v>
+        <v>8.3000000000000001E-3</v>
       </c>
       <c r="I23" s="9" t="s">
         <v>17</v>
@@ -2368,13 +2368,13 @@
         <v>17</v>
       </c>
       <c r="K23" s="9">
-        <v>0</v>
+        <v>8.3000000000000001E-3</v>
       </c>
       <c r="L23" s="8">
-        <v>-100</v>
+        <v>235.9</v>
       </c>
       <c r="M23" s="9">
-        <v>0</v>
+        <v>8.3000000000000001E-3</v>
       </c>
       <c r="N23" s="9" t="s">
         <v>17</v>
@@ -2383,33 +2383,33 @@
         <v>17</v>
       </c>
       <c r="P23" s="9">
-        <v>0</v>
+        <v>8.3000000000000001E-3</v>
       </c>
       <c r="Q23" s="8">
-        <v>-100</v>
+        <v>235.9</v>
       </c>
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B24" s="7">
-        <v>149.5</v>
+        <v>168</v>
       </c>
       <c r="C24" s="7">
-        <v>168</v>
+        <v>236.5</v>
       </c>
       <c r="D24" s="7">
-        <v>177.5</v>
+        <v>254.5</v>
       </c>
       <c r="E24" s="7">
-        <v>140</v>
-      </c>
-      <c r="F24" s="10">
-        <v>18.5</v>
-      </c>
-      <c r="G24" s="10">
-        <v>12.37</v>
+        <v>162.5</v>
+      </c>
+      <c r="F24" s="8">
+        <v>68.5</v>
+      </c>
+      <c r="G24" s="8">
+        <v>40.770000000000003</v>
       </c>
       <c r="H24" s="9">
         <v>0</v>
@@ -2423,7 +2423,7 @@
       <c r="K24" s="9">
         <v>0</v>
       </c>
-      <c r="L24" s="8">
+      <c r="L24" s="10">
         <v>-100</v>
       </c>
       <c r="M24" s="9">
@@ -2438,31 +2438,31 @@
       <c r="P24" s="9">
         <v>0</v>
       </c>
-      <c r="Q24" s="8">
+      <c r="Q24" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>44075</v>
+        <v>44105</v>
       </c>
       <c r="B25" s="7">
-        <v>147</v>
+        <v>149.5</v>
       </c>
       <c r="C25" s="7">
-        <v>149.5</v>
+        <v>168</v>
       </c>
       <c r="D25" s="7">
-        <v>174.5</v>
+        <v>177.5</v>
       </c>
       <c r="E25" s="7">
-        <v>140.5</v>
-      </c>
-      <c r="F25" s="10">
-        <v>2.5</v>
-      </c>
-      <c r="G25" s="10">
-        <v>1.7</v>
+        <v>140</v>
+      </c>
+      <c r="F25" s="8">
+        <v>18.5</v>
+      </c>
+      <c r="G25" s="8">
+        <v>12.37</v>
       </c>
       <c r="H25" s="9">
         <v>0</v>
@@ -2476,7 +2476,7 @@
       <c r="K25" s="9">
         <v>0</v>
       </c>
-      <c r="L25" s="8">
+      <c r="L25" s="10">
         <v>-100</v>
       </c>
       <c r="M25" s="9">
@@ -2491,31 +2491,31 @@
       <c r="P25" s="9">
         <v>0</v>
       </c>
-      <c r="Q25" s="8">
+      <c r="Q25" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>44044</v>
+        <v>44075</v>
       </c>
       <c r="B26" s="7">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="C26" s="7">
-        <v>147</v>
+        <v>149.5</v>
       </c>
       <c r="D26" s="7">
-        <v>156</v>
+        <v>174.5</v>
       </c>
       <c r="E26" s="7">
-        <v>118.5</v>
-      </c>
-      <c r="F26" s="10">
-        <v>25</v>
-      </c>
-      <c r="G26" s="10">
-        <v>20.49</v>
+        <v>140.5</v>
+      </c>
+      <c r="F26" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="G26" s="8">
+        <v>1.7</v>
       </c>
       <c r="H26" s="9">
         <v>0</v>
@@ -2529,7 +2529,7 @@
       <c r="K26" s="9">
         <v>0</v>
       </c>
-      <c r="L26" s="8">
+      <c r="L26" s="10">
         <v>-100</v>
       </c>
       <c r="M26" s="9">
@@ -2544,31 +2544,31 @@
       <c r="P26" s="9">
         <v>0</v>
       </c>
-      <c r="Q26" s="8">
+      <c r="Q26" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="B27" s="7">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="C27" s="7">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="D27" s="7">
-        <v>202</v>
+        <v>156</v>
       </c>
       <c r="E27" s="7">
-        <v>88.6</v>
-      </c>
-      <c r="F27" s="10">
-        <v>30</v>
-      </c>
-      <c r="G27" s="10">
-        <v>32.61</v>
+        <v>118.5</v>
+      </c>
+      <c r="F27" s="8">
+        <v>25</v>
+      </c>
+      <c r="G27" s="8">
+        <v>20.49</v>
       </c>
       <c r="H27" s="9">
         <v>0</v>
@@ -2582,7 +2582,7 @@
       <c r="K27" s="9">
         <v>0</v>
       </c>
-      <c r="L27" s="8">
+      <c r="L27" s="10">
         <v>-100</v>
       </c>
       <c r="M27" s="9">
@@ -2597,31 +2597,31 @@
       <c r="P27" s="9">
         <v>0</v>
       </c>
-      <c r="Q27" s="8">
+      <c r="Q27" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>43983</v>
+        <v>44013</v>
       </c>
       <c r="B28" s="7">
-        <v>79.900000000000006</v>
+        <v>92</v>
       </c>
       <c r="C28" s="7">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="D28" s="7">
-        <v>92</v>
+        <v>202</v>
       </c>
       <c r="E28" s="7">
-        <v>75.400000000000006</v>
-      </c>
-      <c r="F28" s="10">
-        <v>12.1</v>
-      </c>
-      <c r="G28" s="10">
-        <v>15.14</v>
+        <v>88.6</v>
+      </c>
+      <c r="F28" s="8">
+        <v>30</v>
+      </c>
+      <c r="G28" s="8">
+        <v>32.61</v>
       </c>
       <c r="H28" s="9">
         <v>0</v>
@@ -2629,13 +2629,13 @@
       <c r="I28" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J28" s="8">
-        <v>-100</v>
+      <c r="J28" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K28" s="9">
         <v>0</v>
       </c>
-      <c r="L28" s="8">
+      <c r="L28" s="10">
         <v>-100</v>
       </c>
       <c r="M28" s="9">
@@ -2644,37 +2644,37 @@
       <c r="N28" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O28" s="8">
-        <v>-100</v>
+      <c r="O28" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P28" s="9">
         <v>0</v>
       </c>
-      <c r="Q28" s="8">
+      <c r="Q28" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>43952</v>
+        <v>43983</v>
       </c>
       <c r="B29" s="7">
-        <v>62.9</v>
+        <v>79.900000000000006</v>
       </c>
       <c r="C29" s="7">
-        <v>79.900000000000006</v>
+        <v>92</v>
       </c>
       <c r="D29" s="7">
-        <v>83.5</v>
+        <v>92</v>
       </c>
       <c r="E29" s="7">
-        <v>61</v>
-      </c>
-      <c r="F29" s="10">
-        <v>17</v>
-      </c>
-      <c r="G29" s="10">
-        <v>27.03</v>
+        <v>75.400000000000006</v>
+      </c>
+      <c r="F29" s="8">
+        <v>12.1</v>
+      </c>
+      <c r="G29" s="8">
+        <v>15.14</v>
       </c>
       <c r="H29" s="9">
         <v>0</v>
@@ -2682,14 +2682,14 @@
       <c r="I29" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J29" s="9" t="s">
-        <v>17</v>
+      <c r="J29" s="10">
+        <v>-100</v>
       </c>
       <c r="K29" s="9">
         <v>0</v>
       </c>
-      <c r="L29" s="9" t="s">
-        <v>17</v>
+      <c r="L29" s="10">
+        <v>-100</v>
       </c>
       <c r="M29" s="9">
         <v>0</v>
@@ -2697,37 +2697,37 @@
       <c r="N29" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O29" s="9" t="s">
-        <v>17</v>
+      <c r="O29" s="10">
+        <v>-100</v>
       </c>
       <c r="P29" s="9">
         <v>0</v>
       </c>
-      <c r="Q29" s="9" t="s">
-        <v>17</v>
+      <c r="Q29" s="10">
+        <v>-100</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>43922</v>
+        <v>43952</v>
       </c>
       <c r="B30" s="7">
-        <v>63</v>
+        <v>62.9</v>
       </c>
       <c r="C30" s="7">
-        <v>62.9</v>
+        <v>79.900000000000006</v>
       </c>
       <c r="D30" s="7">
-        <v>62.9</v>
+        <v>83.5</v>
       </c>
       <c r="E30" s="7">
-        <v>58.1</v>
+        <v>61</v>
       </c>
       <c r="F30" s="8">
-        <v>-0.1</v>
+        <v>17</v>
       </c>
       <c r="G30" s="8">
-        <v>-0.16</v>
+        <v>27.03</v>
       </c>
       <c r="H30" s="9">
         <v>0</v>
@@ -2762,25 +2762,25 @@
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>43891</v>
+        <v>43922</v>
       </c>
       <c r="B31" s="7">
-        <v>74.989999999999995</v>
+        <v>63</v>
       </c>
       <c r="C31" s="7">
-        <v>63</v>
+        <v>62.9</v>
       </c>
       <c r="D31" s="7">
-        <v>75.77</v>
+        <v>62.9</v>
       </c>
       <c r="E31" s="7">
-        <v>53.71</v>
-      </c>
-      <c r="F31" s="8">
-        <v>-11.99</v>
-      </c>
-      <c r="G31" s="8">
-        <v>-15.99</v>
+        <v>58.1</v>
+      </c>
+      <c r="F31" s="10">
+        <v>-0.1</v>
+      </c>
+      <c r="G31" s="10">
+        <v>-0.16</v>
       </c>
       <c r="H31" s="9">
         <v>0</v>
@@ -2815,25 +2815,25 @@
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>43862</v>
+        <v>43891</v>
       </c>
       <c r="B32" s="7">
-        <v>74.290000000000006</v>
+        <v>74.989999999999995</v>
       </c>
       <c r="C32" s="7">
-        <v>74.989999999999995</v>
+        <v>63</v>
       </c>
       <c r="D32" s="7">
-        <v>74.989999999999995</v>
+        <v>75.77</v>
       </c>
       <c r="E32" s="7">
-        <v>67.45</v>
+        <v>53.71</v>
       </c>
       <c r="F32" s="10">
-        <v>0.7</v>
+        <v>-11.99</v>
       </c>
       <c r="G32" s="10">
-        <v>0.94</v>
+        <v>-15.99</v>
       </c>
       <c r="H32" s="9">
         <v>0</v>
@@ -2868,25 +2868,25 @@
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="B33" s="7">
-        <v>79.989999999999995</v>
+        <v>74.290000000000006</v>
       </c>
       <c r="C33" s="7">
-        <v>74.290000000000006</v>
+        <v>74.989999999999995</v>
       </c>
       <c r="D33" s="7">
-        <v>87.99</v>
+        <v>74.989999999999995</v>
       </c>
       <c r="E33" s="7">
-        <v>66.510000000000005</v>
+        <v>67.45</v>
       </c>
       <c r="F33" s="8">
-        <v>-5.7</v>
+        <v>0.7</v>
       </c>
       <c r="G33" s="8">
-        <v>-7.13</v>
+        <v>0.94</v>
       </c>
       <c r="H33" s="9">
         <v>0</v>
@@ -2921,25 +2921,25 @@
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>43800</v>
+        <v>43831</v>
       </c>
       <c r="B34" s="7">
-        <v>61.99</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="C34" s="7">
-        <v>79.989999999999995</v>
+        <v>74.290000000000006</v>
       </c>
       <c r="D34" s="7">
-        <v>80.989999999999995</v>
+        <v>87.99</v>
       </c>
       <c r="E34" s="7">
-        <v>58</v>
+        <v>66.510000000000005</v>
       </c>
       <c r="F34" s="10">
-        <v>18</v>
+        <v>-5.7</v>
       </c>
       <c r="G34" s="10">
-        <v>29.04</v>
+        <v>-7.13</v>
       </c>
       <c r="H34" s="9">
         <v>0</v>
@@ -2947,14 +2947,14 @@
       <c r="I34" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J34" s="8">
-        <v>-100</v>
+      <c r="J34" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K34" s="9">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="L34" s="10">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="M34" s="9">
         <v>0</v>
@@ -2962,37 +2962,37 @@
       <c r="N34" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O34" s="8">
-        <v>-100</v>
+      <c r="O34" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P34" s="9">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="Q34" s="10">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="Q34" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>43770</v>
+        <v>43800</v>
       </c>
       <c r="B35" s="7">
-        <v>60.59</v>
+        <v>61.99</v>
       </c>
       <c r="C35" s="7">
-        <v>61.99</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="D35" s="7">
-        <v>62</v>
+        <v>80.989999999999995</v>
       </c>
       <c r="E35" s="7">
-        <v>57.71</v>
-      </c>
-      <c r="F35" s="10">
-        <v>1.4</v>
-      </c>
-      <c r="G35" s="10">
-        <v>2.31</v>
+        <v>58</v>
+      </c>
+      <c r="F35" s="8">
+        <v>18</v>
+      </c>
+      <c r="G35" s="8">
+        <v>29.04</v>
       </c>
       <c r="H35" s="9">
         <v>0</v>
@@ -3000,14 +3000,14 @@
       <c r="I35" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J35" s="9" t="s">
-        <v>17</v>
+      <c r="J35" s="10">
+        <v>-100</v>
       </c>
       <c r="K35" s="9">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="L35" s="9" t="s">
-        <v>17</v>
+      <c r="L35" s="8">
+        <v>300</v>
       </c>
       <c r="M35" s="9">
         <v>0</v>
@@ -3015,37 +3015,37 @@
       <c r="N35" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O35" s="9" t="s">
-        <v>17</v>
+      <c r="O35" s="10">
+        <v>-100</v>
       </c>
       <c r="P35" s="9">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="Q35" s="9" t="s">
-        <v>17</v>
+      <c r="Q35" s="8">
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>43739</v>
+        <v>43770</v>
       </c>
       <c r="B36" s="7">
-        <v>61</v>
+        <v>60.59</v>
       </c>
       <c r="C36" s="7">
-        <v>60.59</v>
+        <v>61.99</v>
       </c>
       <c r="D36" s="7">
-        <v>62.49</v>
+        <v>62</v>
       </c>
       <c r="E36" s="7">
-        <v>57.76</v>
+        <v>57.71</v>
       </c>
       <c r="F36" s="8">
-        <v>-0.41</v>
+        <v>1.4</v>
       </c>
       <c r="G36" s="8">
-        <v>-0.67</v>
+        <v>2.31</v>
       </c>
       <c r="H36" s="9">
         <v>0</v>
@@ -3080,25 +3080,25 @@
     </row>
     <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>43709</v>
+        <v>43739</v>
       </c>
       <c r="B37" s="7">
-        <v>58.89</v>
+        <v>61</v>
       </c>
       <c r="C37" s="7">
-        <v>61</v>
+        <v>60.59</v>
       </c>
       <c r="D37" s="7">
-        <v>62.99</v>
+        <v>62.49</v>
       </c>
       <c r="E37" s="7">
-        <v>57.01</v>
+        <v>57.76</v>
       </c>
       <c r="F37" s="10">
-        <v>2.11</v>
+        <v>-0.41</v>
       </c>
       <c r="G37" s="10">
-        <v>3.58</v>
+        <v>-0.67</v>
       </c>
       <c r="H37" s="9">
         <v>0</v>
@@ -3133,25 +3133,25 @@
     </row>
     <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>43678</v>
+        <v>43709</v>
       </c>
       <c r="B38" s="7">
-        <v>60.5</v>
+        <v>58.89</v>
       </c>
       <c r="C38" s="7">
-        <v>58.89</v>
+        <v>61</v>
       </c>
       <c r="D38" s="7">
-        <v>62.09</v>
+        <v>62.99</v>
       </c>
       <c r="E38" s="7">
-        <v>56.7</v>
+        <v>57.01</v>
       </c>
       <c r="F38" s="8">
-        <v>-1.61</v>
+        <v>2.11</v>
       </c>
       <c r="G38" s="8">
-        <v>-2.66</v>
+        <v>3.58</v>
       </c>
       <c r="H38" s="9">
         <v>0</v>
@@ -3186,31 +3186,31 @@
     </row>
     <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>43647</v>
+        <v>43678</v>
       </c>
       <c r="B39" s="7">
-        <v>58.3</v>
+        <v>60.5</v>
       </c>
       <c r="C39" s="7">
-        <v>60.5</v>
+        <v>58.89</v>
       </c>
       <c r="D39" s="7">
-        <v>63.6</v>
+        <v>62.09</v>
       </c>
       <c r="E39" s="7">
-        <v>57.5</v>
+        <v>56.7</v>
       </c>
       <c r="F39" s="10">
-        <v>2.2000000000000002</v>
+        <v>-1.61</v>
       </c>
       <c r="G39" s="10">
-        <v>3.77</v>
+        <v>-2.66</v>
       </c>
       <c r="H39" s="9">
         <v>0</v>
       </c>
-      <c r="I39" s="8">
-        <v>-100</v>
+      <c r="I39" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J39" s="9" t="s">
         <v>17</v>
@@ -3224,8 +3224,8 @@
       <c r="M39" s="9">
         <v>0</v>
       </c>
-      <c r="N39" s="8">
-        <v>-100</v>
+      <c r="N39" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>17</v>
@@ -3239,31 +3239,31 @@
     </row>
     <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>43617</v>
+        <v>43647</v>
       </c>
       <c r="B40" s="7">
         <v>58.3</v>
       </c>
       <c r="C40" s="7">
-        <v>58.3</v>
+        <v>60.5</v>
       </c>
       <c r="D40" s="7">
-        <v>58.9</v>
+        <v>63.6</v>
       </c>
       <c r="E40" s="7">
-        <v>52.7</v>
-      </c>
-      <c r="F40" s="9">
-        <v>0</v>
-      </c>
-      <c r="G40" s="9">
-        <v>0</v>
+        <v>57.5</v>
+      </c>
+      <c r="F40" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G40" s="8">
+        <v>3.77</v>
       </c>
       <c r="H40" s="9">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="I40" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I40" s="10">
+        <v>-100</v>
       </c>
       <c r="J40" s="9" t="s">
         <v>17</v>
@@ -3275,10 +3275,10 @@
         <v>17</v>
       </c>
       <c r="M40" s="9">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="N40" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N40" s="10">
+        <v>-100</v>
       </c>
       <c r="O40" s="9" t="s">
         <v>17</v>
@@ -3292,28 +3292,28 @@
     </row>
     <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>43586</v>
+        <v>43617</v>
       </c>
       <c r="B41" s="7">
-        <v>64</v>
+        <v>58.3</v>
       </c>
       <c r="C41" s="7">
         <v>58.3</v>
       </c>
       <c r="D41" s="7">
-        <v>64</v>
+        <v>58.9</v>
       </c>
       <c r="E41" s="7">
-        <v>56</v>
-      </c>
-      <c r="F41" s="8">
-        <v>-5.7</v>
-      </c>
-      <c r="G41" s="8">
-        <v>-8.91</v>
+        <v>52.7</v>
+      </c>
+      <c r="F41" s="9">
+        <v>0</v>
+      </c>
+      <c r="G41" s="9">
+        <v>0</v>
       </c>
       <c r="H41" s="9">
-        <v>0</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="I41" s="9" t="s">
         <v>17</v>
@@ -3322,13 +3322,13 @@
         <v>17</v>
       </c>
       <c r="K41" s="9">
-        <v>0</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="L41" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M41" s="9">
-        <v>0</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="N41" s="9" t="s">
         <v>17</v>
@@ -3337,7 +3337,7 @@
         <v>17</v>
       </c>
       <c r="P41" s="9">
-        <v>0</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="Q41" s="9" t="s">
         <v>17</v>
@@ -3345,25 +3345,25 @@
     </row>
     <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>43556</v>
+        <v>43586</v>
       </c>
       <c r="B42" s="7">
-        <v>65.5</v>
+        <v>64</v>
       </c>
       <c r="C42" s="7">
+        <v>58.3</v>
+      </c>
+      <c r="D42" s="7">
         <v>64</v>
       </c>
-      <c r="D42" s="7">
-        <v>65.5</v>
-      </c>
       <c r="E42" s="7">
-        <v>60.15</v>
-      </c>
-      <c r="F42" s="8">
-        <v>-1.5</v>
-      </c>
-      <c r="G42" s="8">
-        <v>-2.29</v>
+        <v>56</v>
+      </c>
+      <c r="F42" s="10">
+        <v>-5.7</v>
+      </c>
+      <c r="G42" s="10">
+        <v>-8.91</v>
       </c>
       <c r="H42" s="9">
         <v>0</v>
@@ -3398,25 +3398,25 @@
     </row>
     <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>43525</v>
+        <v>43556</v>
       </c>
       <c r="B43" s="7">
-        <v>65.3</v>
+        <v>65.5</v>
       </c>
       <c r="C43" s="7">
+        <v>64</v>
+      </c>
+      <c r="D43" s="7">
         <v>65.5</v>
       </c>
-      <c r="D43" s="7">
-        <v>66.7</v>
-      </c>
       <c r="E43" s="7">
-        <v>64</v>
+        <v>60.15</v>
       </c>
       <c r="F43" s="10">
-        <v>0.2</v>
+        <v>-1.5</v>
       </c>
       <c r="G43" s="10">
-        <v>0.31</v>
+        <v>-2.29</v>
       </c>
       <c r="H43" s="9">
         <v>0</v>
@@ -3451,25 +3451,25 @@
     </row>
     <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>43497</v>
+        <v>43525</v>
       </c>
       <c r="B44" s="7">
-        <v>65.69</v>
+        <v>65.3</v>
       </c>
       <c r="C44" s="7">
-        <v>65.3</v>
+        <v>65.5</v>
       </c>
       <c r="D44" s="7">
-        <v>66.31</v>
+        <v>66.7</v>
       </c>
       <c r="E44" s="7">
-        <v>61.28</v>
+        <v>64</v>
       </c>
       <c r="F44" s="8">
-        <v>-0.39</v>
+        <v>0.2</v>
       </c>
       <c r="G44" s="8">
-        <v>-0.59</v>
+        <v>0.31</v>
       </c>
       <c r="H44" s="9">
         <v>0</v>
@@ -3504,31 +3504,31 @@
     </row>
     <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>43466</v>
+        <v>43497</v>
       </c>
       <c r="B45" s="7">
-        <v>66.8</v>
+        <v>65.69</v>
       </c>
       <c r="C45" s="7">
-        <v>65.69</v>
+        <v>65.3</v>
       </c>
       <c r="D45" s="7">
-        <v>67.48</v>
+        <v>66.31</v>
       </c>
       <c r="E45" s="7">
-        <v>62.52</v>
-      </c>
-      <c r="F45" s="8">
-        <v>-1.1100000000000001</v>
-      </c>
-      <c r="G45" s="8">
-        <v>-1.66</v>
+        <v>61.28</v>
+      </c>
+      <c r="F45" s="10">
+        <v>-0.39</v>
+      </c>
+      <c r="G45" s="10">
+        <v>-0.59</v>
       </c>
       <c r="H45" s="9">
         <v>0</v>
       </c>
-      <c r="I45" s="8">
-        <v>-100</v>
+      <c r="I45" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J45" s="9" t="s">
         <v>17</v>
@@ -3542,8 +3542,8 @@
       <c r="M45" s="9">
         <v>0</v>
       </c>
-      <c r="N45" s="8">
-        <v>-100</v>
+      <c r="N45" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>17</v>
@@ -3557,131 +3557,131 @@
     </row>
     <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>43435</v>
+        <v>43466</v>
       </c>
       <c r="B46" s="7">
-        <v>69.78</v>
+        <v>66.8</v>
       </c>
       <c r="C46" s="7">
-        <v>66.8</v>
+        <v>65.69</v>
       </c>
       <c r="D46" s="7">
-        <v>69.78</v>
+        <v>67.48</v>
       </c>
       <c r="E46" s="7">
-        <v>64.05</v>
-      </c>
-      <c r="F46" s="8">
-        <v>-2.98</v>
-      </c>
-      <c r="G46" s="8">
-        <v>-4.2699999999999996</v>
+        <v>62.52</v>
+      </c>
+      <c r="F46" s="10">
+        <v>-1.1100000000000001</v>
+      </c>
+      <c r="G46" s="10">
+        <v>-1.66</v>
       </c>
       <c r="H46" s="9">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="I46" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J46" s="8">
-        <v>-27.9</v>
+        <v>0</v>
+      </c>
+      <c r="I46" s="10">
+        <v>-100</v>
+      </c>
+      <c r="J46" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K46" s="9">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="L46" s="8">
-        <v>-94.1</v>
+        <v>0</v>
+      </c>
+      <c r="L46" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="M46" s="9">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="N46" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O46" s="8">
-        <v>-27.9</v>
+        <v>0</v>
+      </c>
+      <c r="N46" s="10">
+        <v>-100</v>
+      </c>
+      <c r="O46" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P46" s="9">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="Q46" s="8">
-        <v>-94.1</v>
+        <v>0</v>
+      </c>
+      <c r="Q46" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
-        <v>43405</v>
+        <v>43435</v>
       </c>
       <c r="B47" s="7">
-        <v>65.98</v>
+        <v>69.78</v>
       </c>
       <c r="C47" s="7">
+        <v>66.8</v>
+      </c>
+      <c r="D47" s="7">
         <v>69.78</v>
       </c>
-      <c r="D47" s="7">
-        <v>72</v>
-      </c>
       <c r="E47" s="7">
-        <v>65.05</v>
+        <v>64.05</v>
       </c>
       <c r="F47" s="10">
-        <v>3.8</v>
+        <v>-2.98</v>
       </c>
       <c r="G47" s="10">
-        <v>5.76</v>
+        <v>-4.2699999999999996</v>
       </c>
       <c r="H47" s="9">
-        <v>0</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="I47" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J47" s="8">
-        <v>-100</v>
+      <c r="J47" s="10">
+        <v>-27.9</v>
       </c>
       <c r="K47" s="9">
-        <v>0</v>
-      </c>
-      <c r="L47" s="8">
-        <v>-100</v>
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="L47" s="10">
+        <v>-94.1</v>
       </c>
       <c r="M47" s="9">
-        <v>0</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="N47" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O47" s="8">
-        <v>-100</v>
+      <c r="O47" s="10">
+        <v>-27.9</v>
       </c>
       <c r="P47" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="8">
-        <v>-100</v>
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="Q47" s="10">
+        <v>-94.1</v>
       </c>
     </row>
     <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
-        <v>43374</v>
+        <v>43405</v>
       </c>
       <c r="B48" s="7">
-        <v>67.5</v>
+        <v>65.98</v>
       </c>
       <c r="C48" s="7">
-        <v>65.98</v>
+        <v>69.78</v>
       </c>
       <c r="D48" s="7">
-        <v>82.1</v>
+        <v>72</v>
       </c>
       <c r="E48" s="7">
-        <v>62</v>
+        <v>65.05</v>
       </c>
       <c r="F48" s="8">
-        <v>-1.52</v>
+        <v>3.8</v>
       </c>
       <c r="G48" s="8">
-        <v>-2.25</v>
+        <v>5.76</v>
       </c>
       <c r="H48" s="9">
         <v>0</v>
@@ -3689,13 +3689,13 @@
       <c r="I48" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J48" s="8">
+      <c r="J48" s="10">
         <v>-100</v>
       </c>
       <c r="K48" s="9">
         <v>0</v>
       </c>
-      <c r="L48" s="8">
+      <c r="L48" s="10">
         <v>-100</v>
       </c>
       <c r="M48" s="9">
@@ -3704,37 +3704,37 @@
       <c r="N48" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O48" s="8">
+      <c r="O48" s="10">
         <v>-100</v>
       </c>
       <c r="P48" s="9">
         <v>0</v>
       </c>
-      <c r="Q48" s="8">
+      <c r="Q48" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
-        <v>43344</v>
+        <v>43374</v>
       </c>
       <c r="B49" s="7">
-        <v>66.599999999999994</v>
+        <v>67.5</v>
       </c>
       <c r="C49" s="7">
-        <v>67.5</v>
+        <v>65.98</v>
       </c>
       <c r="D49" s="7">
-        <v>70</v>
+        <v>82.1</v>
       </c>
       <c r="E49" s="7">
-        <v>63.72</v>
+        <v>62</v>
       </c>
       <c r="F49" s="10">
-        <v>0.9</v>
+        <v>-1.52</v>
       </c>
       <c r="G49" s="10">
-        <v>1.35</v>
+        <v>-2.25</v>
       </c>
       <c r="H49" s="9">
         <v>0</v>
@@ -3742,13 +3742,13 @@
       <c r="I49" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J49" s="8">
+      <c r="J49" s="10">
         <v>-100</v>
       </c>
       <c r="K49" s="9">
         <v>0</v>
       </c>
-      <c r="L49" s="8">
+      <c r="L49" s="10">
         <v>-100</v>
       </c>
       <c r="M49" s="9">
@@ -3757,37 +3757,37 @@
       <c r="N49" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O49" s="8">
+      <c r="O49" s="10">
         <v>-100</v>
       </c>
       <c r="P49" s="9">
         <v>0</v>
       </c>
-      <c r="Q49" s="8">
+      <c r="Q49" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
-        <v>43313</v>
+        <v>43344</v>
       </c>
       <c r="B50" s="7">
-        <v>65.98</v>
+        <v>66.599999999999994</v>
       </c>
       <c r="C50" s="7">
-        <v>66.599999999999994</v>
+        <v>67.5</v>
       </c>
       <c r="D50" s="7">
-        <v>67.5</v>
+        <v>70</v>
       </c>
       <c r="E50" s="7">
-        <v>62.72</v>
-      </c>
-      <c r="F50" s="10">
-        <v>0.62</v>
-      </c>
-      <c r="G50" s="10">
-        <v>0.94</v>
+        <v>63.72</v>
+      </c>
+      <c r="F50" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="G50" s="8">
+        <v>1.35</v>
       </c>
       <c r="H50" s="9">
         <v>0</v>
@@ -3795,13 +3795,13 @@
       <c r="I50" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J50" s="8">
+      <c r="J50" s="10">
         <v>-100</v>
       </c>
       <c r="K50" s="9">
         <v>0</v>
       </c>
-      <c r="L50" s="8">
+      <c r="L50" s="10">
         <v>-100</v>
       </c>
       <c r="M50" s="9">
@@ -3810,37 +3810,37 @@
       <c r="N50" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O50" s="8">
+      <c r="O50" s="10">
         <v>-100</v>
       </c>
       <c r="P50" s="9">
         <v>0</v>
       </c>
-      <c r="Q50" s="8">
+      <c r="Q50" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
-        <v>43282</v>
+        <v>43313</v>
       </c>
       <c r="B51" s="7">
-        <v>65.45</v>
+        <v>65.98</v>
       </c>
       <c r="C51" s="7">
-        <v>65.98</v>
+        <v>66.599999999999994</v>
       </c>
       <c r="D51" s="7">
-        <v>68</v>
+        <v>67.5</v>
       </c>
       <c r="E51" s="7">
-        <v>61.77</v>
-      </c>
-      <c r="F51" s="10">
-        <v>0.53</v>
-      </c>
-      <c r="G51" s="10">
-        <v>0.81</v>
+        <v>62.72</v>
+      </c>
+      <c r="F51" s="8">
+        <v>0.62</v>
+      </c>
+      <c r="G51" s="8">
+        <v>0.94</v>
       </c>
       <c r="H51" s="9">
         <v>0</v>
@@ -3848,13 +3848,13 @@
       <c r="I51" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J51" s="8">
+      <c r="J51" s="10">
         <v>-100</v>
       </c>
       <c r="K51" s="9">
         <v>0</v>
       </c>
-      <c r="L51" s="8">
+      <c r="L51" s="10">
         <v>-100</v>
       </c>
       <c r="M51" s="9">
@@ -3863,37 +3863,37 @@
       <c r="N51" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O51" s="8">
+      <c r="O51" s="10">
         <v>-100</v>
       </c>
       <c r="P51" s="9">
         <v>0</v>
       </c>
-      <c r="Q51" s="8">
+      <c r="Q51" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
-        <v>43252</v>
+        <v>43282</v>
       </c>
       <c r="B52" s="7">
-        <v>62.45</v>
+        <v>65.45</v>
       </c>
       <c r="C52" s="7">
-        <v>65.45</v>
+        <v>65.98</v>
       </c>
       <c r="D52" s="7">
-        <v>66.5</v>
+        <v>68</v>
       </c>
       <c r="E52" s="7">
-        <v>56.53</v>
-      </c>
-      <c r="F52" s="10">
-        <v>3</v>
-      </c>
-      <c r="G52" s="10">
-        <v>4.8</v>
+        <v>61.77</v>
+      </c>
+      <c r="F52" s="8">
+        <v>0.53</v>
+      </c>
+      <c r="G52" s="8">
+        <v>0.81</v>
       </c>
       <c r="H52" s="9">
         <v>0</v>
@@ -3901,13 +3901,13 @@
       <c r="I52" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J52" s="8">
+      <c r="J52" s="10">
         <v>-100</v>
       </c>
       <c r="K52" s="9">
         <v>0</v>
       </c>
-      <c r="L52" s="8">
+      <c r="L52" s="10">
         <v>-100</v>
       </c>
       <c r="M52" s="9">
@@ -3916,420 +3916,420 @@
       <c r="N52" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O52" s="8">
+      <c r="O52" s="10">
         <v>-100</v>
       </c>
       <c r="P52" s="9">
         <v>0</v>
       </c>
-      <c r="Q52" s="8">
+      <c r="Q52" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
-        <v>43221</v>
+        <v>43252</v>
       </c>
       <c r="B53" s="7">
-        <v>69.099999999999994</v>
+        <v>62.45</v>
       </c>
       <c r="C53" s="7">
-        <v>62.45</v>
+        <v>65.45</v>
       </c>
       <c r="D53" s="7">
-        <v>70.34</v>
+        <v>66.5</v>
       </c>
       <c r="E53" s="7">
-        <v>60</v>
+        <v>56.53</v>
       </c>
       <c r="F53" s="8">
-        <v>-6.65</v>
+        <v>3</v>
       </c>
       <c r="G53" s="8">
-        <v>-9.6199999999999992</v>
+        <v>4.8</v>
       </c>
       <c r="H53" s="9">
         <v>0</v>
       </c>
-      <c r="I53" s="8">
-        <v>-100</v>
-      </c>
-      <c r="J53" s="8">
+      <c r="I53" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J53" s="10">
         <v>-100</v>
       </c>
       <c r="K53" s="9">
         <v>0</v>
       </c>
-      <c r="L53" s="8">
+      <c r="L53" s="10">
         <v>-100</v>
       </c>
       <c r="M53" s="9">
         <v>0</v>
       </c>
-      <c r="N53" s="8">
-        <v>-100</v>
-      </c>
-      <c r="O53" s="8">
+      <c r="N53" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O53" s="10">
         <v>-100</v>
       </c>
       <c r="P53" s="9">
         <v>0</v>
       </c>
-      <c r="Q53" s="8">
+      <c r="Q53" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
-        <v>43191</v>
+        <v>43221</v>
       </c>
       <c r="B54" s="7">
-        <v>68.5</v>
+        <v>69.099999999999994</v>
       </c>
       <c r="C54" s="7">
-        <v>69.099999999999994</v>
+        <v>62.45</v>
       </c>
       <c r="D54" s="7">
-        <v>71.05</v>
+        <v>70.34</v>
       </c>
       <c r="E54" s="7">
-        <v>64.06</v>
+        <v>60</v>
       </c>
       <c r="F54" s="10">
-        <v>0.6</v>
+        <v>-6.65</v>
       </c>
       <c r="G54" s="10">
-        <v>0.88</v>
+        <v>-9.6199999999999992</v>
       </c>
       <c r="H54" s="9">
         <v>0</v>
       </c>
-      <c r="I54" s="8">
-        <v>-100</v>
-      </c>
-      <c r="J54" s="8">
+      <c r="I54" s="10">
+        <v>-100</v>
+      </c>
+      <c r="J54" s="10">
         <v>-100</v>
       </c>
       <c r="K54" s="9">
         <v>0</v>
       </c>
-      <c r="L54" s="8">
+      <c r="L54" s="10">
         <v>-100</v>
       </c>
       <c r="M54" s="9">
         <v>0</v>
       </c>
-      <c r="N54" s="8">
-        <v>-100</v>
-      </c>
-      <c r="O54" s="8">
+      <c r="N54" s="10">
+        <v>-100</v>
+      </c>
+      <c r="O54" s="10">
         <v>-100</v>
       </c>
       <c r="P54" s="9">
         <v>0</v>
       </c>
-      <c r="Q54" s="8">
+      <c r="Q54" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
-        <v>43160</v>
+        <v>43191</v>
       </c>
       <c r="B55" s="7">
-        <v>66.98</v>
+        <v>68.5</v>
       </c>
       <c r="C55" s="7">
-        <v>68.5</v>
+        <v>69.099999999999994</v>
       </c>
       <c r="D55" s="7">
-        <v>74.73</v>
+        <v>71.05</v>
       </c>
       <c r="E55" s="7">
-        <v>59</v>
-      </c>
-      <c r="F55" s="10">
-        <v>1.52</v>
-      </c>
-      <c r="G55" s="10">
-        <v>2.27</v>
+        <v>64.06</v>
+      </c>
+      <c r="F55" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="G55" s="8">
+        <v>0.88</v>
       </c>
       <c r="H55" s="9">
         <v>0</v>
       </c>
-      <c r="I55" s="8">
-        <v>-100</v>
-      </c>
-      <c r="J55" s="8">
+      <c r="I55" s="10">
+        <v>-100</v>
+      </c>
+      <c r="J55" s="10">
         <v>-100</v>
       </c>
       <c r="K55" s="9">
         <v>0</v>
       </c>
-      <c r="L55" s="8">
+      <c r="L55" s="10">
         <v>-100</v>
       </c>
       <c r="M55" s="9">
         <v>0</v>
       </c>
-      <c r="N55" s="8">
-        <v>-100</v>
-      </c>
-      <c r="O55" s="8">
+      <c r="N55" s="10">
+        <v>-100</v>
+      </c>
+      <c r="O55" s="10">
         <v>-100</v>
       </c>
       <c r="P55" s="9">
         <v>0</v>
       </c>
-      <c r="Q55" s="8">
+      <c r="Q55" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
-        <v>43132</v>
+        <v>43160</v>
       </c>
       <c r="B56" s="7">
-        <v>72.8</v>
+        <v>66.98</v>
       </c>
       <c r="C56" s="7">
-        <v>66.98</v>
+        <v>68.5</v>
       </c>
       <c r="D56" s="7">
-        <v>73</v>
+        <v>74.73</v>
       </c>
       <c r="E56" s="7">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F56" s="8">
-        <v>-5.82</v>
+        <v>1.52</v>
       </c>
       <c r="G56" s="8">
-        <v>-7.99</v>
+        <v>2.27</v>
       </c>
       <c r="H56" s="9">
         <v>0</v>
       </c>
-      <c r="I56" s="8">
-        <v>-100</v>
-      </c>
-      <c r="J56" s="8">
+      <c r="I56" s="10">
+        <v>-100</v>
+      </c>
+      <c r="J56" s="10">
         <v>-100</v>
       </c>
       <c r="K56" s="9">
         <v>0</v>
       </c>
-      <c r="L56" s="8">
+      <c r="L56" s="10">
         <v>-100</v>
       </c>
       <c r="M56" s="9">
         <v>0</v>
       </c>
-      <c r="N56" s="8">
-        <v>-100</v>
-      </c>
-      <c r="O56" s="8">
+      <c r="N56" s="10">
+        <v>-100</v>
+      </c>
+      <c r="O56" s="10">
         <v>-100</v>
       </c>
       <c r="P56" s="9">
         <v>0</v>
       </c>
-      <c r="Q56" s="8">
+      <c r="Q56" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
-        <v>43101</v>
+        <v>43132</v>
       </c>
       <c r="B57" s="7">
-        <v>65</v>
+        <v>72.8</v>
       </c>
       <c r="C57" s="7">
-        <v>72.8</v>
+        <v>66.98</v>
       </c>
       <c r="D57" s="7">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E57" s="7">
-        <v>65.5</v>
+        <v>64</v>
       </c>
       <c r="F57" s="10">
-        <v>7.8</v>
+        <v>-5.82</v>
       </c>
       <c r="G57" s="10">
-        <v>12</v>
+        <v>-7.99</v>
       </c>
       <c r="H57" s="9">
         <v>0</v>
       </c>
-      <c r="I57" s="8">
-        <v>-100</v>
-      </c>
-      <c r="J57" s="8">
+      <c r="I57" s="10">
+        <v>-100</v>
+      </c>
+      <c r="J57" s="10">
         <v>-100</v>
       </c>
       <c r="K57" s="9">
         <v>0</v>
       </c>
-      <c r="L57" s="8">
+      <c r="L57" s="10">
         <v>-100</v>
       </c>
       <c r="M57" s="9">
         <v>0</v>
       </c>
-      <c r="N57" s="8">
-        <v>-100</v>
-      </c>
-      <c r="O57" s="8">
+      <c r="N57" s="10">
+        <v>-100</v>
+      </c>
+      <c r="O57" s="10">
         <v>-100</v>
       </c>
       <c r="P57" s="9">
         <v>0</v>
       </c>
-      <c r="Q57" s="8">
+      <c r="Q57" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
-        <v>43070</v>
+        <v>43101</v>
       </c>
       <c r="B58" s="7">
-        <v>55.77</v>
+        <v>65</v>
       </c>
       <c r="C58" s="7">
-        <v>65</v>
+        <v>72.8</v>
       </c>
       <c r="D58" s="7">
-        <v>65.98</v>
+        <v>80</v>
       </c>
       <c r="E58" s="7">
-        <v>53.3</v>
-      </c>
-      <c r="F58" s="10">
-        <v>9.23</v>
-      </c>
-      <c r="G58" s="10">
-        <v>16.55</v>
+        <v>65.5</v>
+      </c>
+      <c r="F58" s="8">
+        <v>7.8</v>
+      </c>
+      <c r="G58" s="8">
+        <v>12</v>
       </c>
       <c r="H58" s="9">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="I58" s="8">
-        <v>-1.1399999999999999</v>
-      </c>
-      <c r="J58" s="8">
-        <v>-7.52</v>
+        <v>0</v>
+      </c>
+      <c r="I58" s="10">
+        <v>-100</v>
+      </c>
+      <c r="J58" s="10">
+        <v>-100</v>
       </c>
       <c r="K58" s="9">
-        <v>1.0500000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="L58" s="10">
-        <v>1028</v>
+        <v>-100</v>
       </c>
       <c r="M58" s="9">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="N58" s="8">
-        <v>-1.1399999999999999</v>
-      </c>
-      <c r="O58" s="8">
-        <v>-7.52</v>
+        <v>0</v>
+      </c>
+      <c r="N58" s="10">
+        <v>-100</v>
+      </c>
+      <c r="O58" s="10">
+        <v>-100</v>
       </c>
       <c r="P58" s="9">
-        <v>1.0500000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="10">
-        <v>1028</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
-        <v>43040</v>
+        <v>43070</v>
       </c>
       <c r="B59" s="7">
-        <v>55.18</v>
+        <v>55.77</v>
       </c>
       <c r="C59" s="7">
-        <v>55.77</v>
+        <v>65</v>
       </c>
       <c r="D59" s="7">
-        <v>56</v>
+        <v>65.98</v>
       </c>
       <c r="E59" s="7">
-        <v>52.5</v>
-      </c>
-      <c r="F59" s="10">
-        <v>0.59</v>
-      </c>
-      <c r="G59" s="10">
-        <v>1.07</v>
+        <v>53.3</v>
+      </c>
+      <c r="F59" s="8">
+        <v>9.23</v>
+      </c>
+      <c r="G59" s="8">
+        <v>16.55</v>
       </c>
       <c r="H59" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="I59" s="9">
-        <v>0</v>
-      </c>
-      <c r="J59" s="9" t="s">
-        <v>17</v>
+      <c r="I59" s="10">
+        <v>-1.1399999999999999</v>
+      </c>
+      <c r="J59" s="10">
+        <v>-7.52</v>
       </c>
       <c r="K59" s="9">
-        <v>9.5999999999999992E-3</v>
-      </c>
-      <c r="L59" s="9" t="s">
-        <v>17</v>
+        <v>1.0500000000000001E-2</v>
+      </c>
+      <c r="L59" s="8">
+        <v>1028</v>
       </c>
       <c r="M59" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="N59" s="9">
-        <v>0</v>
-      </c>
-      <c r="O59" s="9" t="s">
-        <v>17</v>
+      <c r="N59" s="10">
+        <v>-1.1399999999999999</v>
+      </c>
+      <c r="O59" s="10">
+        <v>-7.52</v>
       </c>
       <c r="P59" s="9">
-        <v>9.5999999999999992E-3</v>
-      </c>
-      <c r="Q59" s="9" t="s">
-        <v>17</v>
+        <v>1.0500000000000001E-2</v>
+      </c>
+      <c r="Q59" s="8">
+        <v>1028</v>
       </c>
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
-        <v>43009</v>
+        <v>43040</v>
       </c>
       <c r="B60" s="7">
-        <v>54</v>
+        <v>55.18</v>
       </c>
       <c r="C60" s="7">
-        <v>55.18</v>
+        <v>55.77</v>
       </c>
       <c r="D60" s="7">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E60" s="7">
-        <v>52</v>
-      </c>
-      <c r="F60" s="10">
-        <v>1.18</v>
-      </c>
-      <c r="G60" s="10">
-        <v>2.19</v>
+        <v>52.5</v>
+      </c>
+      <c r="F60" s="8">
+        <v>0.59</v>
+      </c>
+      <c r="G60" s="8">
+        <v>1.07</v>
       </c>
       <c r="H60" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="I60" s="8">
-        <v>-1.1299999999999999</v>
+      <c r="I60" s="9">
+        <v>0</v>
       </c>
       <c r="J60" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K60" s="9">
-        <v>8.8000000000000005E-3</v>
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="L60" s="9" t="s">
         <v>17</v>
@@ -4337,14 +4337,14 @@
       <c r="M60" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="N60" s="8">
-        <v>-1.1299999999999999</v>
+      <c r="N60" s="9">
+        <v>0</v>
       </c>
       <c r="O60" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P60" s="9">
-        <v>8.8000000000000005E-3</v>
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="Q60" s="9" t="s">
         <v>17</v>
@@ -4352,37 +4352,37 @@
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
-        <v>42979</v>
+        <v>43009</v>
       </c>
       <c r="B61" s="7">
-        <v>53.8</v>
+        <v>54</v>
       </c>
       <c r="C61" s="7">
-        <v>54</v>
+        <v>55.18</v>
       </c>
       <c r="D61" s="7">
-        <v>59.2</v>
+        <v>58</v>
       </c>
       <c r="E61" s="7">
-        <v>50.35</v>
-      </c>
-      <c r="F61" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="G61" s="10">
-        <v>0.37</v>
+        <v>52</v>
+      </c>
+      <c r="F61" s="8">
+        <v>1.18</v>
+      </c>
+      <c r="G61" s="8">
+        <v>2.19</v>
       </c>
       <c r="H61" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
       <c r="I61" s="10">
-        <v>1.1399999999999999</v>
+        <v>-1.1299999999999999</v>
       </c>
       <c r="J61" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K61" s="9">
-        <v>7.9000000000000008E-3</v>
+        <v>8.8000000000000005E-3</v>
       </c>
       <c r="L61" s="9" t="s">
         <v>17</v>
@@ -4391,13 +4391,13 @@
         <v>8.9999999999999998E-4</v>
       </c>
       <c r="N61" s="10">
-        <v>1.1399999999999999</v>
+        <v>-1.1299999999999999</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P61" s="9">
-        <v>7.9000000000000008E-3</v>
+        <v>8.8000000000000005E-3</v>
       </c>
       <c r="Q61" s="9" t="s">
         <v>17</v>
@@ -4405,37 +4405,37 @@
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
-        <v>42948</v>
+        <v>42979</v>
       </c>
       <c r="B62" s="7">
-        <v>56.88</v>
+        <v>53.8</v>
       </c>
       <c r="C62" s="7">
-        <v>53.8</v>
+        <v>54</v>
       </c>
       <c r="D62" s="7">
-        <v>56.98</v>
+        <v>59.2</v>
       </c>
       <c r="E62" s="7">
-        <v>52</v>
+        <v>50.35</v>
       </c>
       <c r="F62" s="8">
-        <v>-3.08</v>
+        <v>0.2</v>
       </c>
       <c r="G62" s="8">
-        <v>-5.41</v>
+        <v>0.37</v>
       </c>
       <c r="H62" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="I62" s="9">
-        <v>0</v>
+      <c r="I62" s="8">
+        <v>1.1399999999999999</v>
       </c>
       <c r="J62" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K62" s="9">
-        <v>7.0000000000000001E-3</v>
+        <v>7.9000000000000008E-3</v>
       </c>
       <c r="L62" s="9" t="s">
         <v>17</v>
@@ -4443,14 +4443,14 @@
       <c r="M62" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="N62" s="9">
-        <v>0</v>
+      <c r="N62" s="8">
+        <v>1.1399999999999999</v>
       </c>
       <c r="O62" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P62" s="9">
-        <v>7.0000000000000001E-3</v>
+        <v>7.9000000000000008E-3</v>
       </c>
       <c r="Q62" s="9" t="s">
         <v>17</v>
@@ -4458,37 +4458,37 @@
     </row>
     <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
-        <v>42917</v>
+        <v>42948</v>
       </c>
       <c r="B63" s="7">
-        <v>63.45</v>
+        <v>56.88</v>
       </c>
       <c r="C63" s="7">
-        <v>56.88</v>
+        <v>53.8</v>
       </c>
       <c r="D63" s="7">
-        <v>63.5</v>
+        <v>56.98</v>
       </c>
       <c r="E63" s="7">
-        <v>47.5</v>
-      </c>
-      <c r="F63" s="8">
-        <v>-6.57</v>
-      </c>
-      <c r="G63" s="8">
-        <v>-10.35</v>
+        <v>52</v>
+      </c>
+      <c r="F63" s="10">
+        <v>-3.08</v>
+      </c>
+      <c r="G63" s="10">
+        <v>-5.41</v>
       </c>
       <c r="H63" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="I63" s="8">
-        <v>-1.1299999999999999</v>
+      <c r="I63" s="9">
+        <v>0</v>
       </c>
       <c r="J63" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K63" s="9">
-        <v>6.1999999999999998E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="L63" s="9" t="s">
         <v>17</v>
@@ -4496,14 +4496,14 @@
       <c r="M63" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="N63" s="8">
-        <v>-1.1299999999999999</v>
+      <c r="N63" s="9">
+        <v>0</v>
       </c>
       <c r="O63" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P63" s="9">
-        <v>6.1999999999999998E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="Q63" s="9" t="s">
         <v>17</v>
@@ -4511,37 +4511,37 @@
     </row>
     <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
-        <v>42887</v>
+        <v>42917</v>
       </c>
       <c r="B64" s="7">
-        <v>60.5</v>
+        <v>63.45</v>
       </c>
       <c r="C64" s="7">
-        <v>63.45</v>
+        <v>56.88</v>
       </c>
       <c r="D64" s="7">
-        <v>69.5</v>
+        <v>63.5</v>
       </c>
       <c r="E64" s="7">
-        <v>60</v>
+        <v>47.5</v>
       </c>
       <c r="F64" s="10">
-        <v>2.95</v>
+        <v>-6.57</v>
       </c>
       <c r="G64" s="10">
-        <v>4.88</v>
+        <v>-10.35</v>
       </c>
       <c r="H64" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
       <c r="I64" s="10">
-        <v>1.1399999999999999</v>
+        <v>-1.1299999999999999</v>
       </c>
       <c r="J64" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K64" s="9">
-        <v>5.3E-3</v>
+        <v>6.1999999999999998E-3</v>
       </c>
       <c r="L64" s="9" t="s">
         <v>17</v>
@@ -4550,13 +4550,13 @@
         <v>8.9999999999999998E-4</v>
       </c>
       <c r="N64" s="10">
-        <v>1.1399999999999999</v>
+        <v>-1.1299999999999999</v>
       </c>
       <c r="O64" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P64" s="9">
-        <v>5.3E-3</v>
+        <v>6.1999999999999998E-3</v>
       </c>
       <c r="Q64" s="9" t="s">
         <v>17</v>
@@ -4564,37 +4564,37 @@
     </row>
     <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
-        <v>42856</v>
+        <v>42887</v>
       </c>
       <c r="B65" s="7">
-        <v>67.5</v>
+        <v>60.5</v>
       </c>
       <c r="C65" s="7">
-        <v>60.5</v>
+        <v>63.45</v>
       </c>
       <c r="D65" s="7">
-        <v>67.48</v>
+        <v>69.5</v>
       </c>
       <c r="E65" s="7">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F65" s="8">
-        <v>-7</v>
+        <v>2.95</v>
       </c>
       <c r="G65" s="8">
-        <v>-10.37</v>
+        <v>4.88</v>
       </c>
       <c r="H65" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="I65" s="9">
-        <v>0</v>
+      <c r="I65" s="8">
+        <v>1.1399999999999999</v>
       </c>
       <c r="J65" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K65" s="9">
-        <v>4.4000000000000003E-3</v>
+        <v>5.3E-3</v>
       </c>
       <c r="L65" s="9" t="s">
         <v>17</v>
@@ -4602,14 +4602,14 @@
       <c r="M65" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="N65" s="9">
-        <v>0</v>
+      <c r="N65" s="8">
+        <v>1.1399999999999999</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P65" s="9">
-        <v>4.4000000000000003E-3</v>
+        <v>5.3E-3</v>
       </c>
       <c r="Q65" s="9" t="s">
         <v>17</v>
@@ -4617,37 +4617,37 @@
     </row>
     <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
-        <v>42826</v>
+        <v>42856</v>
       </c>
       <c r="B66" s="7">
-        <v>72.099999999999994</v>
+        <v>67.5</v>
       </c>
       <c r="C66" s="7">
-        <v>67.5</v>
+        <v>60.5</v>
       </c>
       <c r="D66" s="7">
-        <v>75.78</v>
+        <v>67.48</v>
       </c>
       <c r="E66" s="7">
-        <v>61.51</v>
-      </c>
-      <c r="F66" s="8">
-        <v>-4.5999999999999996</v>
-      </c>
-      <c r="G66" s="8">
-        <v>-6.38</v>
+        <v>57</v>
+      </c>
+      <c r="F66" s="10">
+        <v>-7</v>
+      </c>
+      <c r="G66" s="10">
+        <v>-10.37</v>
       </c>
       <c r="H66" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="I66" s="8">
-        <v>-1.1299999999999999</v>
+      <c r="I66" s="9">
+        <v>0</v>
       </c>
       <c r="J66" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K66" s="9">
-        <v>3.5000000000000001E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="L66" s="9" t="s">
         <v>17</v>
@@ -4655,14 +4655,14 @@
       <c r="M66" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="N66" s="8">
-        <v>-1.1299999999999999</v>
+      <c r="N66" s="9">
+        <v>0</v>
       </c>
       <c r="O66" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P66" s="9">
-        <v>3.5000000000000001E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="Q66" s="9" t="s">
         <v>17</v>
@@ -4670,37 +4670,37 @@
     </row>
     <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
-        <v>42795</v>
+        <v>42826</v>
       </c>
       <c r="B67" s="7">
-        <v>84.29</v>
+        <v>72.099999999999994</v>
       </c>
       <c r="C67" s="7">
-        <v>72.099999999999994</v>
+        <v>67.5</v>
       </c>
       <c r="D67" s="7">
-        <v>84.5</v>
+        <v>75.78</v>
       </c>
       <c r="E67" s="7">
-        <v>68.02</v>
-      </c>
-      <c r="F67" s="8">
-        <v>-12.19</v>
-      </c>
-      <c r="G67" s="8">
-        <v>-14.46</v>
+        <v>61.51</v>
+      </c>
+      <c r="F67" s="10">
+        <v>-4.5999999999999996</v>
+      </c>
+      <c r="G67" s="10">
+        <v>-6.38</v>
       </c>
       <c r="H67" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="I67" s="9">
-        <v>0</v>
+      <c r="I67" s="10">
+        <v>-1.1299999999999999</v>
       </c>
       <c r="J67" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K67" s="9">
-        <v>2.7000000000000001E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="L67" s="9" t="s">
         <v>17</v>
@@ -4708,14 +4708,14 @@
       <c r="M67" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="N67" s="9">
-        <v>0</v>
+      <c r="N67" s="10">
+        <v>-1.1299999999999999</v>
       </c>
       <c r="O67" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P67" s="9">
-        <v>2.7000000000000001E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="Q67" s="9" t="s">
         <v>17</v>
@@ -4723,37 +4723,37 @@
     </row>
     <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
-        <v>42767</v>
+        <v>42795</v>
       </c>
       <c r="B68" s="7">
-        <v>91.2</v>
+        <v>84.29</v>
       </c>
       <c r="C68" s="7">
-        <v>84.29</v>
+        <v>72.099999999999994</v>
       </c>
       <c r="D68" s="7">
-        <v>100</v>
+        <v>84.5</v>
       </c>
       <c r="E68" s="7">
-        <v>81.7</v>
-      </c>
-      <c r="F68" s="8">
-        <v>-7.91</v>
-      </c>
-      <c r="G68" s="8">
-        <v>-8.58</v>
+        <v>68.02</v>
+      </c>
+      <c r="F68" s="10">
+        <v>-12.19</v>
+      </c>
+      <c r="G68" s="10">
+        <v>-14.46</v>
       </c>
       <c r="H68" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="I68" s="8">
-        <v>-2.2200000000000002</v>
+      <c r="I68" s="9">
+        <v>0</v>
       </c>
       <c r="J68" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K68" s="9">
-        <v>1.8E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="L68" s="9" t="s">
         <v>17</v>
@@ -4761,14 +4761,14 @@
       <c r="M68" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="N68" s="8">
-        <v>-2.2200000000000002</v>
+      <c r="N68" s="9">
+        <v>0</v>
       </c>
       <c r="O68" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P68" s="9">
-        <v>1.8E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="Q68" s="9" t="s">
         <v>17</v>
@@ -4776,37 +4776,37 @@
     </row>
     <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
-        <v>42736</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E69" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F69" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G69" s="9" t="s">
-        <v>17</v>
+        <v>42767</v>
+      </c>
+      <c r="B69" s="7">
+        <v>91.2</v>
+      </c>
+      <c r="C69" s="7">
+        <v>84.29</v>
+      </c>
+      <c r="D69" s="7">
+        <v>100</v>
+      </c>
+      <c r="E69" s="7">
+        <v>81.7</v>
+      </c>
+      <c r="F69" s="10">
+        <v>-7.91</v>
+      </c>
+      <c r="G69" s="10">
+        <v>-8.58</v>
       </c>
       <c r="H69" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="I69" s="9" t="s">
-        <v>17</v>
+      <c r="I69" s="10">
+        <v>-2.2200000000000002</v>
       </c>
       <c r="J69" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K69" s="9">
-        <v>8.9999999999999998E-4</v>
+        <v>1.8E-3</v>
       </c>
       <c r="L69" s="9" t="s">
         <v>17</v>
@@ -4814,16 +4814,69 @@
       <c r="M69" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="N69" s="9" t="s">
-        <v>17</v>
+      <c r="N69" s="10">
+        <v>-2.2200000000000002</v>
       </c>
       <c r="O69" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P69" s="9">
+        <v>1.8E-3</v>
+      </c>
+      <c r="Q69" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A70" s="6">
+        <v>42736</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G70" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H70" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="Q69" s="9" t="s">
+      <c r="I70" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J70" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K70" s="9">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="L70" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M70" s="9">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="N70" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O70" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P70" s="9">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="Q70" s="9" t="s">
         <v>17</v>
       </c>
     </row>
